--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088364</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1257,6 +1287,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088419</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1354,6 +1389,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088421</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,6 +1491,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1548,6 +1593,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1645,6 +1695,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1742,6 +1797,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088392</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1839,6 +1899,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098615</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333192</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2067,6 +2137,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098588</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088328</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2342,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088349</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2359,6 +2444,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088372</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098603</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2553,6 +2648,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098604</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,8 +2750,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119088377</v>
+        <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>92036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Nävertjärn Pålsträsket Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784601</v>
+        <v>783548</v>
       </c>
       <c r="R2" t="n">
-        <v>7291402</v>
+        <v>7294601</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,54 +786,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088377</t>
+          <t>https://artportalen.se/Sighting/136309467</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119088398</v>
+        <v>136309466</v>
       </c>
       <c r="B3" t="n">
-        <v>83173</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Nävertjärn Pålsträsket Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784606</v>
+        <v>783505</v>
       </c>
       <c r="R3" t="n">
-        <v>7291521</v>
+        <v>7294594</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088398</t>
+          <t>https://artportalen.se/Sighting/136309466</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119088399</v>
+        <v>136309465</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Nävertjärn Pålsträsket Älvsbyn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784591</v>
+        <v>783504</v>
       </c>
       <c r="R4" t="n">
-        <v>7291480</v>
+        <v>7294597</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -950,12 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,7 +998,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,16 +1015,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088399</t>
+          <t>https://artportalen.se/Sighting/136309465</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119088406</v>
+        <v>119088377</v>
       </c>
       <c r="B5" t="n">
-        <v>83173</v>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784565</v>
+        <v>784601</v>
       </c>
       <c r="R5" t="n">
-        <v>7291485</v>
+        <v>7291402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1085,38 +1117,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088406</t>
+          <t>https://artportalen.se/Sighting/119088377</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119088364</v>
+        <v>119088398</v>
       </c>
       <c r="B6" t="n">
-        <v>95962</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784562</v>
+        <v>784606</v>
       </c>
       <c r="R6" t="n">
-        <v>7291491</v>
+        <v>7291521</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1202,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,38 +1220,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088364</t>
+          <t>https://artportalen.se/Sighting/119088398</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119088419</v>
+        <v>119088399</v>
       </c>
       <c r="B7" t="n">
-        <v>97231</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784604</v>
+        <v>784591</v>
       </c>
       <c r="R7" t="n">
-        <v>7291524</v>
+        <v>7291480</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,6 +1305,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,38 +1323,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088419</t>
+          <t>https://artportalen.se/Sighting/119088399</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119088421</v>
+        <v>119088406</v>
       </c>
       <c r="B8" t="n">
-        <v>97231</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784610</v>
+        <v>784565</v>
       </c>
       <c r="R8" t="n">
-        <v>7291391</v>
+        <v>7291485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1391,16 +1426,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088421</t>
+          <t>https://artportalen.se/Sighting/119088406</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119098620</v>
+        <v>119088364</v>
       </c>
       <c r="B9" t="n">
-        <v>97231</v>
+        <v>95962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1443,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>2387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784632</v>
+        <v>784562</v>
       </c>
       <c r="R9" t="n">
-        <v>7291530</v>
+        <v>7291491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,24 +1517,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098620</t>
+          <t>https://artportalen.se/Sighting/119088364</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119098621</v>
+        <v>119088419</v>
       </c>
       <c r="B10" t="n">
         <v>97231</v>
@@ -1530,14 +1565,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784588</v>
+        <v>784604</v>
       </c>
       <c r="R10" t="n">
-        <v>7291503</v>
+        <v>7291524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,49 +1619,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098621</t>
+          <t>https://artportalen.se/Sighting/119088419</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119088390</v>
+        <v>119088421</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784631</v>
+        <v>784610</v>
       </c>
       <c r="R11" t="n">
-        <v>7291541</v>
+        <v>7291391</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,51 +1732,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088390</t>
+          <t>https://artportalen.se/Sighting/119088421</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119088392</v>
+        <v>119098620</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>97231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Altertjärnen, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784602</v>
+        <v>784632</v>
       </c>
       <c r="R12" t="n">
-        <v>7291443</v>
+        <v>7291530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,49 +1823,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088392</t>
+          <t>https://artportalen.se/Sighting/119098620</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119098615</v>
+        <v>119098621</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>97231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784586</v>
+        <v>784588</v>
       </c>
       <c r="R13" t="n">
-        <v>7291480</v>
+        <v>7291503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,13 +1936,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098615</t>
+          <t>https://artportalen.se/Sighting/119098621</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130333192</v>
+        <v>119088390</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1936,19 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>pålsträskheden1, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784895</v>
+        <v>784631</v>
       </c>
       <c r="R14" t="n">
-        <v>7291537</v>
+        <v>7291541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,12 +2007,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,99 +2021,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>gammal senvuxen</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # gammal senvuxen</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130333192</t>
+          <t>https://artportalen.se/Sighting/119088390</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119098588</v>
+        <v>119088392</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784600</v>
+        <v>784602</v>
       </c>
       <c r="R15" t="n">
-        <v>7291450</v>
+        <v>7291443</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,62 +2129,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098588</t>
+          <t>https://artportalen.se/Sighting/119088392</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119088328</v>
+        <v>119098615</v>
       </c>
       <c r="B16" t="n">
-        <v>57258</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Altertjärnen, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784565</v>
+        <v>784586</v>
       </c>
       <c r="R16" t="n">
-        <v>7291489</v>
+        <v>7291480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,62 +2231,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088328</t>
+          <t>https://artportalen.se/Sighting/119098615</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119088349</v>
+        <v>130333192</v>
       </c>
       <c r="B17" t="n">
-        <v>58790</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>pålsträskheden1, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784601</v>
+        <v>784895</v>
       </c>
       <c r="R17" t="n">
-        <v>7291520</v>
+        <v>7291537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,12 +2316,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,65 +2334,95 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>gammal senvuxen</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # gammal senvuxen</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088349</t>
+          <t>https://artportalen.se/Sighting/130333192</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119088372</v>
+        <v>119098588</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Altertjärn B, Nb</t>
+          <t>Altertjärnen, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784604</v>
+        <v>784600</v>
       </c>
       <c r="R18" t="n">
-        <v>7291525</v>
+        <v>7291450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,62 +2469,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119088372</t>
+          <t>https://artportalen.se/Sighting/119098588</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119098603</v>
+        <v>119088328</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>57258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784632</v>
+        <v>784565</v>
       </c>
       <c r="R19" t="n">
-        <v>7291539</v>
+        <v>7291489</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,62 +2571,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098603</t>
+          <t>https://artportalen.se/Sighting/119088328</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119098604</v>
+        <v>119088349</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>58790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784612</v>
+        <v>784601</v>
       </c>
       <c r="R20" t="n">
-        <v>7291496</v>
+        <v>7291520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,30 +2667,31 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119098604</t>
+          <t>https://artportalen.se/Sighting/119088349</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119098605</v>
+        <v>119088372</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -2687,14 +2722,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Altertjärnen, Nb</t>
+          <t>Altertjärn B, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784566</v>
+        <v>784604</v>
       </c>
       <c r="R21" t="n">
-        <v>7291504</v>
+        <v>7291525</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,16 +2776,322 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088372</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119098603</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Altertjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>784632</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7291539</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098603</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119098604</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Altertjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>784612</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7291496</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119098604</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119098605</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Altertjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>784566</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7291504</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119098605</t>
         </is>
@@ -2778,6 +3119,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1092-2023 artfynd.xlsx
+++ b/artfynd/S 1092-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309467</v>
       </c>
       <c r="B2" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136309466</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136309465</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
